--- a/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
+++ b/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
@@ -525,7 +525,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06T08:53:37Z</t>
+          <t>2026-10-06T10:36:48Z</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-06T08:53:37Z</t>
+          <t>2026-10-06T10:36:48Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>

--- a/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
+++ b/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
@@ -13,16 +13,18 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gap Analysis" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Claims" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All figures" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI provenance" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Methodology" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$3:$B$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$3:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'5 Dimensions'!$A$1:$E$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SDG Alignment'!$A$1:$G$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Gap Analysis'!$A$1:$F$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Claims'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All figures'!$A$1:$G$53</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Methodology'!$A$1:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Claims'!$A$1:$F$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All figures'!$A$1:$G$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'AI provenance'!$A$13:$F$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Methodology'!$A$1:$B$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -455,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -525,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-06T10:36:48Z</t>
+          <t>2026-10-07T00:37:37Z</t>
         </is>
       </c>
     </row>
@@ -620,17 +622,53 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>AI disclosure</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 3 of 21 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Methodology version</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.1.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Methodology config hash</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>8fabf9b5a7e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Export schema</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:B16"/>
+  <autoFilter ref="A3:B19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -861,15 +899,15 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Decent Work and Economic Growth</t>
+          <t>Affordable and Clean Energy</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
-        <v>33.5</v>
+        <v>41.8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -883,26 +921,26 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>OI6213, OI8869</t>
+          <t>OI2764, PI7954</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8.1, 8.10, 8.2, 8.3, 8.5, 8.6, 8.7, 8.8</t>
+          <t>7.1, 7.2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Affordable and Clean Energy</t>
+          <t>Climate Action</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>32.5</v>
+        <v>36.7</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -914,24 +952,28 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>OI2764</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7.1, 7.2</t>
+          <t>13.1, 13.2, 13.3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Industry, Innovation and Infrastructure</t>
+          <t>Decent Work and Economic Growth</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>30.5</v>
+        <v>32.3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,26 +987,26 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OI8869</t>
+          <t>OI6213, OI8869</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>9.1, 9.3</t>
+          <t>8.1, 8.10, 8.2, 8.3, 8.5, 8.6, 8.7, 8.8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Climate Action</t>
+          <t>No Poverty</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>30</v>
+        <v>27.5</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -979,21 +1021,21 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>13.1, 13.2, 13.3</t>
+          <t>1.4, 1.5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>No Poverty</t>
+          <t>Industry, Innovation and Infrastructure</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>27.5</v>
+        <v>26.5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1005,10 +1047,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>OI8869</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1.4, 1.5</t>
+          <t>9.1, 9.3</t>
         </is>
       </c>
     </row>
@@ -1126,15 +1172,15 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gender Equality</t>
+          <t>Good Health and Well-being</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1146,28 +1192,20 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>OI6213</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>5.1, 5.2, 5.5</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Good Health and Well-being</t>
+          <t>Gender Equality</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>15</v>
+        <v>12.7</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1179,21 +1217,29 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>OI6213</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5.1, 5.2, 5.5</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Quality Education</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Reduced Inequalities</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="n">
-        <v>14.8</v>
-      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>low</t>
@@ -1204,24 +1250,16 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>OI6213</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>10.1, 10.2, 10.3, 10.c</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Quality Education</t>
+          <t>Reduced Inequalities</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -1238,7 +1276,11 @@
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>10.1, 10.2, 10.3, 10.c</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1794,7 +1836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1802,6 +1844,7 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1830,6 +1873,11 @@
           <t>Mapped metrics</t>
         </is>
       </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Extracted by</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1849,6 +1897,11 @@
         <v>0.3</v>
       </c>
       <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1872,6 +1925,11 @@
           <t>PI7954</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1895,6 +1953,11 @@
           <t>OI2764</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1918,6 +1981,11 @@
           <t>OI8869, OI6213</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1937,6 +2005,11 @@
         <v>0.3</v>
       </c>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1956,6 +2029,11 @@
         <v>0.35</v>
       </c>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1975,6 +2053,11 @@
         <v>0.3</v>
       </c>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1994,6 +2077,11 @@
         <v>0.3</v>
       </c>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2013,9 +2101,14 @@
         <v>0.25</v>
       </c>
       <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E10"/>
+  <autoFilter ref="A1:F10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2026,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2107,7 +2200,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-06T10:36:48Z</t>
+          <t>2026-10-07T00:37:37Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -2116,68 +2209,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5D</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Overall Grade</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1.6/5.0</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
+          <t>AI disclosure</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 3 of 21 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>5D</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>What</t>
+          <t>Methodology</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.0/5.0</t>
+          <t>1.1.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Reporting 1 metrics (1 theme-specific, 16 available)</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>score</t>
-        </is>
-      </c>
+          <t>config 8fabf9b5a7e2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2187,21 +2256,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Who</t>
+          <t>Overall Grade</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.8/5.0</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Reporting 3 metrics (0 theme-specific, 1 available)</t>
+          <t>1.6/5.0</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>5</v>
@@ -2220,21 +2289,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>How Much</t>
+          <t>What</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.7/5.0</t>
+          <t>2.0/5.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Scale=1.7, Depth=1.7, Duration=1.7</t>
+          <t>Reporting 1 metrics (1 theme-specific, 16 available)</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>5</v>
@@ -2253,21 +2322,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Contribution</t>
+          <t>Who</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.5/5.0</t>
+          <t>1.8/5.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Depth=1.5, Duration=1.5</t>
+          <t>Reporting 3 metrics (0 theme-specific, 1 available)</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>5</v>
@@ -2286,21 +2355,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Risk</t>
+          <t>How Much</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.2/5.0</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Estimated from sector/description (4 metrics available to track) (adverse impact penalty -0.3)</t>
+          <t>1.7/5.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Scale=1.7, Depth=1.7, Duration=1.7</t>
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>5</v>
@@ -2314,29 +2383,29 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>5D</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SDG 8</t>
+          <t>Contribution</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>33.5/100</t>
+          <t>1.5/5.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>medium | metrics: OI6213,OI8869</t>
+          <t>Depth=1.5, Duration=1.5</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>33.5</v>
+        <v>1.5</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -2347,29 +2416,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>5D</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SDG 7</t>
+          <t>Risk</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>32.5/100</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">medium | metrics: </t>
+          <t>1.2/5.0</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Estimated from sector/description (4 metrics available to track) (adverse impact penalty -0.3)</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>32.5</v>
+        <v>1.2</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -2385,21 +2454,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SDG 9</t>
+          <t>SDG 7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>30.5/100</t>
+          <t>41.8/100</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>medium | metrics: OI8869</t>
+          <t>medium | metrics: OI2764,PI7954</t>
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>30.5</v>
+        <v>41.8</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>100</v>
@@ -2423,16 +2492,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>30.0/100</t>
+          <t>36.7/100</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">medium | metrics: </t>
+          <t>medium | metrics: OI2764</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>30</v>
+        <v>36.7</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>100</v>
@@ -2451,21 +2520,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SDG 1</t>
+          <t>SDG 8</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>27.5/100</t>
+          <t>32.3/100</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">medium | metrics: </t>
+          <t>medium | metrics: OI6213,OI8869</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>27.5</v>
+        <v>32.3</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>100</v>
@@ -2484,12 +2553,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SDG 2</t>
+          <t>SDG 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>25.0/100</t>
+          <t>27.5/100</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2498,7 +2567,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>100</v>
@@ -2517,21 +2586,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SDG 11</t>
+          <t>SDG 9</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20.0/100</t>
+          <t>26.5/100</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">medium | metrics: </t>
+          <t>medium | metrics: OI8869</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>20</v>
+        <v>26.5</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>100</v>
@@ -2550,21 +2619,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SDG 6</t>
+          <t>SDG 2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>17.5/100</t>
+          <t>25.0/100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">low | metrics: </t>
+          <t xml:space="preserve">medium | metrics: </t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>17.5</v>
+        <v>25</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>100</v>
@@ -2583,21 +2652,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SDG 15</t>
+          <t>SDG 11</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>17.5/100</t>
+          <t>20.0/100</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">low | metrics: </t>
+          <t xml:space="preserve">medium | metrics: </t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="F18" s="6" t="n">
         <v>100</v>
@@ -2616,21 +2685,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SDG 5</t>
+          <t>SDG 6</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16.0/100</t>
+          <t>17.5/100</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>low | metrics: OI6213</t>
+          <t xml:space="preserve">low | metrics: </t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="F19" s="6" t="n">
         <v>100</v>
@@ -2649,12 +2718,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SDG 3</t>
+          <t>SDG 15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15.0/100</t>
+          <t>17.5/100</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2663,7 +2732,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>100</v>
@@ -2682,21 +2751,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SDG 10</t>
+          <t>SDG 3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>14.8/100</t>
+          <t>15.0/100</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>low | metrics: OI6213</t>
+          <t xml:space="preserve">low | metrics: </t>
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>100</v>
@@ -2715,21 +2784,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>SDG 5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10.0/100</t>
+          <t>12.7/100</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">low | metrics: </t>
+          <t>low | metrics: OI6213</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>10</v>
+        <v>12.7</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>100</v>
@@ -2748,7 +2817,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SDG 12</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2781,7 +2850,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SDG 16</t>
+          <t>SDG 10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2814,12 +2883,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SDG 14</t>
+          <t>SDG 12</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7.5/100</t>
+          <t>10.0/100</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2828,7 +2897,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>100</v>
@@ -2842,87 +2911,101 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Greenwashing</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Risk score</t>
+          <t>SDG 16</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>46.0/100</t>
+          <t>10.0/100</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Moderate Risk</t>
+          <t xml:space="preserve">low | metrics: </t>
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="F26" s="6" t="n">
         <v>100</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>risk</t>
+          <t>score</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>SDG 14</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>17.6%</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>7.5/100</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low | metrics: </t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
-        <v>17.6</v>
+        <v>7.5</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>100</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>score</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Greenwashing</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OD4091</t>
+          <t>Risk score</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>46.0/100</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Social and Environmental Targets</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
+          <t>Moderate Risk</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>risk</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2932,20 +3015,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OI1075</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MISSING</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Board of Directors: Total</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>17.6%</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" s="5" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2955,7 +3044,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>OI1479</t>
+          <t>OD4091</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2965,7 +3054,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Greenhouse Gas Emissions: Total</t>
+          <t>Social and Environmental Targets</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -2978,7 +3067,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>OI1571</t>
+          <t>OI1075</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2988,7 +3077,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Full-time Employees: Female Managers</t>
+          <t>Board of Directors: Total</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3001,7 +3090,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OI1582</t>
+          <t>OI1479</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3011,7 +3100,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Wage Equity</t>
+          <t>Greenhouse Gas Emissions: Total</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3024,7 +3113,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OI3757</t>
+          <t>OI1571</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3034,7 +3123,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Occupational Injuries</t>
+          <t>Full-time Employees: Female Managers</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3047,7 +3136,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OI4112</t>
+          <t>OI1582</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3057,7 +3146,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Greenhouse Gas Emissions: Direct (Scope 1)</t>
+          <t>Wage Equity</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3070,7 +3159,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OI4724</t>
+          <t>OI3757</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3080,7 +3169,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Workers Earning a Living Wage or Higher</t>
+          <t>Occupational Injuries</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -3093,7 +3182,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OI4732</t>
+          <t>OI4112</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3103,7 +3192,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Social and Environmental Performance Reporting</t>
+          <t>Greenhouse Gas Emissions: Direct (Scope 1)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3116,7 +3205,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OI5049</t>
+          <t>OI4724</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3126,7 +3215,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Client Feedback System</t>
+          <t>Workers Earning a Living Wage or Higher</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3139,7 +3228,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PD1504</t>
+          <t>OI4732</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3149,7 +3238,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Energy Capacity of Products Sold</t>
+          <t>Social and Environmental Performance Reporting</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -3162,7 +3251,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PI2822</t>
+          <t>OI5049</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3172,7 +3261,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Client Individuals: Provided New Access</t>
+          <t>Client Feedback System</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -3185,7 +3274,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PI4060</t>
+          <t>PD1504</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3195,7 +3284,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Client Individuals: Total</t>
+          <t>Energy Capacity of Products Sold</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -3208,7 +3297,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PI5842</t>
+          <t>PI2822</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3218,7 +3307,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Energy Generated for Sale: Renewable</t>
+          <t>Client Individuals: Provided New Access</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -3231,27 +3320,20 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OI2764</t>
+          <t>PI4060</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>20,000 tCO2e</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Greenhouse Gas Emissions Avoided</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>20000</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>tCO2e</t>
-        </is>
-      </c>
+          <t>Client Individuals: Total</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3261,27 +3343,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OI6213</t>
+          <t>PI5842</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>127 (derived: 41% of 310)</t>
+          <t>MISSING</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Full-time Employees: Female</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>127</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>(derived: 41% of 310)</t>
-        </is>
-      </c>
+          <t>Energy Generated for Sale: Renewable</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3291,67 +3366,81 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OI8869</t>
+          <t>OI2764</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>20,000 tCO2e</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Permanent Employees: Total</t>
+          <t>Greenhouse Gas Emissions Avoided</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>310</v>
-      </c>
-      <c r="G44" t="inlineStr"/>
+        <v>20000</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>tCO2e</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Claim</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Around 25 million people in Kenya still light their homes with kerosene or have no electricity at all.</t>
+          <t>OI6213</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>127 (derived: 41% of 310)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">metrics: </t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>Full-time Employees: Female</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>(derived: 41% of 310)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Claim</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>outcome</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>We have connected 42,000 households across 14 counties, replacing kerosene lamps and reducing household energy spend by 30%.</t>
+          <t>OI8869</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>310</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>metrics: PI7954</t>
-        </is>
+          <t>Permanent Employees: Total</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>310</v>
       </c>
       <c r="G46" t="inlineStr"/>
     </row>
@@ -3363,17 +3452,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>outcome</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Our systems avoided an estimated 20,000 tCO2e in 2024.</t>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>Around 25 million people in Kenya still light their homes with kerosene or have no electricity at all.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>metrics: OI2764</t>
+          <t xml:space="preserve">metrics: </t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -3391,12 +3480,12 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>Repayment rates stay above 92% and we employ 310 staff, of whom 41% are women.</t>
+          <t>We have connected 42,000 households across 14 counties, replacing kerosene lamps and reducing household energy spend by 30%.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>metrics: OI8869,OI6213</t>
+          <t>metrics: PI7954</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -3412,14 +3501,14 @@
           <t>outcome</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>Who we serve 62% of our customers live below the national poverty line according to the Poverty Probability Index, and 71% had no electricity before buying from us.</t>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Our systems avoided an estimated 20,000 tCO2e in 2024.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">metrics: </t>
+          <t>metrics: OI2764</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -3437,12 +3526,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>A 2025 study by an independent evaluator compared customers with a matched control group and found 18% higher evening study hours for children and lower reported respiratory symptoms.</t>
+          <t>Repayment rates stay above 92% and we employ 310 staff, of whom 41% are women.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">metrics: </t>
+          <t>metrics: OI8869,OI6213</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -3460,7 +3549,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Over-indebtedness: we cap instalments at 10% of estimated household income and offer payment holidays after crop failures.</t>
+          <t>Who we serve 62% of our customers live below the national poverty line according to the Poverty Probability Index, and 71% had no electricity before buying from us.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3478,12 +3567,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>intent</t>
+          <t>outcome</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Over the next three years we target 150,000 connected households and 80,000 tCO2e avoided per year, and we report against IRIS+, SDG 7/1/13 and the GOGLA impact metrics.</t>
+          <t>A 2025 study by an independent evaluator compared customers with a matched control group and found 18% higher evening study hours for children and lower reported respiratory symptoms.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3501,23 +3590,69 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>outcome</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Over-indebtedness: we cap instalments at 10% of estimated household income and offer payment holidays after crop failures.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metrics: </t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>intent</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Over the next three years we target 150,000 connected households and 80,000 tCO2e avoided per year, and we report against IRIS+, SDG 7/1/13 and the GOGLA impact metrics.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">metrics: </t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Claim</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>output</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="C55" s="3" t="inlineStr">
         <is>
           <t>Our carbon methodology is verified by a third-party auditor under Gold Standard rules.</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t xml:space="preserve">metrics: </t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G53"/>
+  <autoFilter ref="A1:G55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3528,7 +3663,830 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AI disclosure</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 3 of 21 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Claim extraction</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Score calculation</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Metric / SDG tagging</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Narrative drafting</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Generative AI used</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Scores estimated from text</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3 of 21</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Human review</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>not recorded</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Regulation</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>EU AI Act Art 50 transparency (Regulation (EU) 2024/1689 as amended by Regulation (EU) 2026/1744)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Figure</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Stage</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Estimated</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Five Dimensions: what</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>evidence: partial</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Five Dimensions: who</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>evidence: evidence-based</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Five Dimensions: how much</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>evidence: estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Five Dimensions: contribution</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>evidence: estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Five Dimensions: risk</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>evidence: estimated</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SDG 7 alignment</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SDG 13 alignment</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SDG 8 alignment</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SDG 1 alignment</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SDG 9 alignment</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SDG 2 alignment</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SDG 11 alignment</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SDG 6 alignment</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SDG 15 alignment</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SDG 3 alignment</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SDG 5 alignment</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SDG 4 alignment</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SDG 10 alignment</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SDG 12 alignment</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SDG 16 alignment</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SDG 14 alignment</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>deterministic</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>basis: core_set</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>9 impact claims</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>extraction</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>IRIS+ / SDG mapping of claims</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>tagging</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>rules</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A13:F36"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -3567,31 +4525,31 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>Scores (1–5) for What, Who, How Much, Contribution and Risk come from reported metrics where available and from document text otherwise.</t>
+          <t>Each dimension scores 1–5: coverage of the theme's IRIS+ reference set × 4.5 + 0.5 when any metric is reported, plus up to 0.5 for extra metrics. A dimension stays at or below 2.5 until 3 metrics hit its reference set; text-only inference is clamped to 0.5–2.5. Grades: A ≥ 4.5, B+ ≥ 3.5, B ≥ 3.0, B- ≥ 2.5, C+ ≥ 2.0, C ≥ 1.5, D ≥ 1.0.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SDGs</t>
+          <t>5D penalties</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Scores (0–100) combine goal-specific metric coverage and inference from the business and impact themes; cross-cutting metrics count at reduced weight. 'Material' marks goals the business model directly drives.</t>
+          <t>Risk loses 0.3 per unmitigated adverse impact (max 1.5) and 0.5 per exclusion flag (max 1.0).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Gap analysis</t>
+          <t>SDGs</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Coverage is the share of the sector's IRIS+ core metric set the company reports.</t>
+          <t>Each goal scores 0–100: up to 60 points from goal-specific metric coverage (metrics tagged to 6+ goals count at 0.4 weight), up to 25 from the business description and up to 15 from impact themes. High confidence needs ≥50 points and at least one goal-specific metric. Own-footprint metrics (OI4112, OI9604, OI1479, OI1697) are disclosure, not contribution, and count at the reduced weight.</t>
         </is>
       </c>
     </row>
@@ -3603,48 +4561,84 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Risk (0–100) weights claim–metric gaps (30%), missing negative impacts (20%), vague language (20%), selective reporting (15%) and lack of verification (15%). 60+ is flagged for review.</t>
+          <t>Risk (0–100) weights claim–metric gaps (30%), missing negative impacts (20%), vague language (20%), selective reporting (15%) and lack of verification (15%). Bands: ≤20 Genuine Impact Leader; ≤40 Substantive with Gaps; ≤60 Moderate Risk; ≤80 High Risk; ≤100 Probable Greenwashing.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>IC gate</t>
+          <t>Version</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Applies the fund thesis thresholds. Failures caused by missing data are reported as insufficient evidence, not as a negative finding.</t>
+          <t>Methodology v1.1.0 · config 8fabf9b5a7e2 (effective 2026-10-07).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Standards</t>
+          <t>Gap analysis</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>IRIS+ 5.3c catalog, IMP Five Dimensions, UN SDG framework (17 goals, 169 targets).</t>
+          <t>Coverage is the share of the sector's IRIS+ core metric set the company reports.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>IC gate</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Applies the fund thesis thresholds. Failures caused by missing data are reported as insufficient evidence, not as a negative finding.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Standards</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IRIS+ 5.3c catalog, IMP Five Dimensions, UN SDG framework (17 goals, 169 targets).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Schema</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Export schema version 1.0. Numeric cells are numbers; '—' marks values that were not reported.</t>
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI use</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 3 of 21 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B9"/>
+  <autoFilter ref="A1:B12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
+++ b/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-07T00:37:37Z</t>
+          <t>2026-10-07T00:55:02Z</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-07T00:37:37Z</t>
+          <t>2026-10-07T00:55:02Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>

--- a/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
+++ b/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-07T00:55:02Z</t>
+          <t>2026-10-07T01:08:41Z</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Reporting 1 metrics (1 theme-specific, 16 available)</t>
+          <t>1 metric reported · 1 of 16 reference metrics</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Reporting 3 metrics (0 theme-specific, 1 available)</t>
+          <t>3 metrics reported · 0 of 1 reference metrics</t>
         </is>
       </c>
     </row>
@@ -817,7 +817,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Estimated from sector/description (4 metrics available to track) (adverse impact penalty -0.3)</t>
+          <t>Estimated from sector/description · 4 reference metrics to track (adverse impact penalty -0.3)</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-07T00:55:02Z</t>
+          <t>2026-10-07T01:08:41Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Reporting 1 metrics (1 theme-specific, 16 available)</t>
+          <t>1 metric reported · 1 of 16 reference metrics</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
@@ -2332,7 +2332,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Reporting 3 metrics (0 theme-specific, 1 available)</t>
+          <t>3 metrics reported · 0 of 1 reference metrics</t>
         </is>
       </c>
       <c r="E8" s="5" t="n">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Estimated from sector/description (4 metrics available to track) (adverse impact penalty -0.3)</t>
+          <t>Estimated from sector/description · 4 reference metrics to track (adverse impact penalty -0.3)</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">

--- a/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
+++ b/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
@@ -19,10 +19,10 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$3:$B$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'5 Dimensions'!$A$1:$E$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SDG Alignment'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SDG Alignment'!$A$1:$G$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Gap Analysis'!$A$1:$F$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Claims'!$A$1:$F$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All figures'!$A$1:$G$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All figures'!$A$1:$G$54</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'AI provenance'!$A$13:$F$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Methodology'!$A$1:$B$12</definedName>
   </definedNames>
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-07T01:08:41Z</t>
+          <t>2026-10-08T15:56:23Z</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="12">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -627,7 +627,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 3 of 21 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
+          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 2 of 21 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.2.0</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>8fabf9b5a7e2</t>
+          <t>ae3e77ecaccf</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B2" s="4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="C3" t="n">
         <v>3</v>
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -817,7 +817,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Estimated from sector/description · 4 reference metrics to track (adverse impact penalty -0.3)</t>
+          <t>Estimated from sector/description · 4 reference metrics to track</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -848,7 +848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -965,15 +965,15 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Decent Work and Economic Growth</t>
+          <t>Gender Equality</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>32.3</v>
+        <v>30.2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,12 +987,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>OI6213, OI8869</t>
+          <t>OI6213</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.1, 8.10, 8.2, 8.3, 8.5, 8.6, 8.7, 8.8</t>
+          <t>5.1, 5.2, 5.5</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>27.5</v>
+        <v>30</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,15 +1027,15 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Industry, Innovation and Infrastructure</t>
+          <t>Decent Work and Economic Growth</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>26.5</v>
+        <v>27.3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1049,26 +1049,26 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>OI8869</t>
+          <t>OI6213, OI8869</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>9.1, 9.3</t>
+          <t>8.1, 8.10, 8.2, 8.3, 8.5, 8.6, 8.7, 8.8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Zero Hunger</t>
+          <t>Industry, Innovation and Infrastructure</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>25</v>
+        <v>26.5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1080,10 +1080,14 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>OI8869</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.1, 2.3, 2.4</t>
+          <t>9.1, 9.3</t>
         </is>
       </c>
     </row>
@@ -1118,11 +1122,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Clean Water and Sanitation</t>
+          <t>Zero Hunger</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
@@ -1141,21 +1145,21 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6.1, 6.2, 6.4</t>
+          <t>2.1, 2.3, 2.4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Life on Land</t>
+          <t>Good Health and Well-being</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1172,15 +1176,15 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Good Health and Well-being</t>
+          <t>Quality Education</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1197,15 +1201,15 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gender Equality</t>
+          <t>Clean Water and Sanitation</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>12.7</v>
+        <v>10</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1217,24 +1221,20 @@
           <t>no</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>OI6213</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5.1, 5.2, 5.5</t>
+          <t>6.1, 6.2, 6.4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Quality Education</t>
+          <t>Reduced Inequalities</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
@@ -1251,15 +1251,19 @@
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>10.1, 10.2, 10.3, 10.c</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Reduced Inequalities</t>
+          <t>Responsible Consumption and Production</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
@@ -1278,17 +1282,17 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>10.1, 10.2, 10.3, 10.c</t>
+          <t>12.2, 12.3, 12.4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Responsible Consumption and Production</t>
+          <t>Life on Land</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
@@ -1305,11 +1309,7 @@
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>12.2, 12.3, 12.4</t>
-        </is>
-      </c>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1336,33 +1336,8 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Life Below Water</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1510,12 +1485,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OD4091</t>
+          <t>PI5842</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Social and Environmental Targets</t>
+          <t>Energy Generated for Sale: Renewable</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -1533,12 +1508,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OI1075</t>
+          <t>PD1504</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Board of Directors: Total</t>
+          <t>Energy Capacity of Products Sold</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -1556,12 +1531,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OI1479</t>
+          <t>OI5049</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Greenhouse Gas Emissions: Total</t>
+          <t>Client Feedback System</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -1579,12 +1554,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OI1571</t>
+          <t>PI2822</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Full-time Employees: Female Managers</t>
+          <t>Client Individuals: Provided New Access</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1602,12 +1577,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>OI1582</t>
+          <t>OI3757</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wage Equity</t>
+          <t>Occupational Injuries</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -1625,12 +1600,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OI3757</t>
+          <t>PI4060</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Occupational Injuries</t>
+          <t>Client Individuals: Total</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -1648,12 +1623,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OI4112</t>
+          <t>OI4724</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Greenhouse Gas Emissions: Direct (Scope 1)</t>
+          <t>Workers Earning a Living Wage or Higher</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -1671,12 +1646,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>OI4724</t>
+          <t>OI1479</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Workers Earning a Living Wage or Higher</t>
+          <t>Greenhouse Gas Emissions: Total</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -1694,12 +1669,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>OI4732</t>
+          <t>OI1582</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Social and Environmental Performance Reporting</t>
+          <t>Wage Equity</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -1717,12 +1692,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OI5049</t>
+          <t>OI4112</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Client Feedback System</t>
+          <t>Greenhouse Gas Emissions: Direct (Scope 1)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -1740,12 +1715,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PD1504</t>
+          <t>OD4091</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Energy Capacity of Products Sold</t>
+          <t>Social and Environmental Targets</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -1763,12 +1738,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PI2822</t>
+          <t>OI1075</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Client Individuals: Provided New Access</t>
+          <t>Board of Directors: Total</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -1786,12 +1761,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PI4060</t>
+          <t>OI1571</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Client Individuals: Total</t>
+          <t>Full-time Employees: Female Managers</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -1809,12 +1784,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PI5842</t>
+          <t>OI4732</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Energy Generated for Sale: Renewable</t>
+          <t>Social and Environmental Performance Reporting</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -2119,7 +2094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2200,7 +2175,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-07T01:08:41Z</t>
+          <t>2026-10-08T15:56:23Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -2219,7 +2194,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 3 of 21 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
+          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 2 of 21 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -2238,12 +2213,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.1.0</t>
+          <t>1.2.0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>config 8fabf9b5a7e2</t>
+          <t>config ae3e77ecaccf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -2266,11 +2241,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.6/5.0</t>
+          <t>1.8/5.0</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>5</v>
@@ -2294,7 +2269,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2.0/5.0</t>
+          <t>2.5/5.0</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2303,7 +2278,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>5</v>
@@ -2327,7 +2302,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.8/5.0</t>
+          <t>2.5/5.0</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2336,7 +2311,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>5</v>
@@ -2426,16 +2401,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.2/5.0</t>
+          <t>1.0/5.0</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Estimated from sector/description · 4 reference metrics to track (adverse impact penalty -0.3)</t>
+          <t>Estimated from sector/description · 4 reference metrics to track</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>5</v>
@@ -2520,21 +2495,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SDG 8</t>
+          <t>SDG 5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>32.3/100</t>
+          <t>30.2/100</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>medium | metrics: OI6213,OI8869</t>
+          <t>medium | metrics: OI6213</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>32.3</v>
+        <v>30.2</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>100</v>
@@ -2558,7 +2533,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>27.5/100</t>
+          <t>30.0/100</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2567,7 +2542,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>27.5</v>
+        <v>30</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>100</v>
@@ -2586,21 +2561,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SDG 9</t>
+          <t>SDG 8</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>26.5/100</t>
+          <t>27.3/100</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>medium | metrics: OI8869</t>
+          <t>medium | metrics: OI6213,OI8869</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>26.5</v>
+        <v>27.3</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>100</v>
@@ -2619,21 +2594,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SDG 2</t>
+          <t>SDG 9</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>25.0/100</t>
+          <t>26.5/100</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">medium | metrics: </t>
+          <t>medium | metrics: OI8869</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>25</v>
+        <v>26.5</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>100</v>
@@ -2685,7 +2660,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SDG 6</t>
+          <t>SDG 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2718,12 +2693,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SDG 15</t>
+          <t>SDG 3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>17.5/100</t>
+          <t>10.0/100</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2732,7 +2707,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>100</v>
@@ -2751,12 +2726,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SDG 3</t>
+          <t>SDG 4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>15.0/100</t>
+          <t>10.0/100</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2765,7 +2740,7 @@
         </is>
       </c>
       <c r="E21" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F21" s="6" t="n">
         <v>100</v>
@@ -2784,21 +2759,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SDG 5</t>
+          <t>SDG 6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>12.7/100</t>
+          <t>10.0/100</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>low | metrics: OI6213</t>
+          <t xml:space="preserve">low | metrics: </t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>12.7</v>
+        <v>10</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>100</v>
@@ -2817,7 +2792,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SDG 4</t>
+          <t>SDG 10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2850,7 +2825,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SDG 10</t>
+          <t>SDG 12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2883,7 +2858,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SDG 12</t>
+          <t>SDG 15</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2944,66 +2919,62 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>Greenwashing</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SDG 14</t>
+          <t>Risk score</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>7.5/100</t>
+          <t>34.0/100</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">low | metrics: </t>
+          <t>Substantive with Gaps</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>7.5</v>
+        <v>34</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>100</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>risk</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Greenwashing</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Risk score</t>
+          <t>Coverage</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>46.0/100</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Moderate Risk</t>
-        </is>
-      </c>
+          <t>17.6%</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
       <c r="E28" s="5" t="n">
-        <v>46</v>
+        <v>17.6</v>
       </c>
       <c r="F28" s="6" t="n">
         <v>100</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>risk</t>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -3015,26 +2986,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Coverage</t>
+          <t>PI5842</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17.6%</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" s="5" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="F29" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
+          <t>MISSING</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Energy Generated for Sale: Renewable</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3044,7 +3009,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>OD4091</t>
+          <t>PD1504</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3054,7 +3019,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Social and Environmental Targets</t>
+          <t>Energy Capacity of Products Sold</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3067,7 +3032,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>OI1075</t>
+          <t>OI5049</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3077,7 +3042,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Board of Directors: Total</t>
+          <t>Client Feedback System</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3090,7 +3055,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OI1479</t>
+          <t>PI2822</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3100,7 +3065,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Greenhouse Gas Emissions: Total</t>
+          <t>Client Individuals: Provided New Access</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3113,7 +3078,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OI1571</t>
+          <t>OI3757</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3123,7 +3088,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Full-time Employees: Female Managers</t>
+          <t>Occupational Injuries</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3136,7 +3101,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OI1582</t>
+          <t>PI4060</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3146,7 +3111,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Wage Equity</t>
+          <t>Client Individuals: Total</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3159,7 +3124,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OI3757</t>
+          <t>OI4724</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3169,7 +3134,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Occupational Injuries</t>
+          <t>Workers Earning a Living Wage or Higher</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -3182,7 +3147,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OI4112</t>
+          <t>OI1479</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3192,7 +3157,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Greenhouse Gas Emissions: Direct (Scope 1)</t>
+          <t>Greenhouse Gas Emissions: Total</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3205,7 +3170,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OI4724</t>
+          <t>OI1582</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3215,7 +3180,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Workers Earning a Living Wage or Higher</t>
+          <t>Wage Equity</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -3228,7 +3193,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OI4732</t>
+          <t>OI4112</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3238,7 +3203,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Social and Environmental Performance Reporting</t>
+          <t>Greenhouse Gas Emissions: Direct (Scope 1)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -3251,7 +3216,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OI5049</t>
+          <t>OD4091</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3261,7 +3226,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Client Feedback System</t>
+          <t>Social and Environmental Targets</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -3274,7 +3239,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PD1504</t>
+          <t>OI1075</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3284,7 +3249,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Energy Capacity of Products Sold</t>
+          <t>Board of Directors: Total</t>
         </is>
       </c>
       <c r="G40" t="inlineStr"/>
@@ -3297,7 +3262,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PI2822</t>
+          <t>OI1571</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3307,7 +3272,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Client Individuals: Provided New Access</t>
+          <t>Full-time Employees: Female Managers</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -3320,7 +3285,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PI4060</t>
+          <t>OI4732</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3330,7 +3295,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Client Individuals: Total</t>
+          <t>Social and Environmental Performance Reporting</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -3343,20 +3308,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>PI5842</t>
+          <t>OI2764</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>20,000 tCO2e</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Energy Generated for Sale: Renewable</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>Greenhouse Gas Emissions Avoided</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>tCO2e</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3366,25 +3338,25 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>OI2764</t>
+          <t>OI6213</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>20,000 tCO2e</t>
+          <t>127 (derived: 41% of 310)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Greenhouse Gas Emissions Avoided</t>
+          <t>Full-time Employees: Female</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">
-        <v>20000</v>
+        <v>127</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>tCO2e</t>
+          <t>(derived: 41% of 310)</t>
         </is>
       </c>
     </row>
@@ -3396,51 +3368,44 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OI6213</t>
+          <t>OI8869</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>127 (derived: 41% of 310)</t>
+          <t>310</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Full-time Employees: Female</t>
+          <t>Permanent Employees: Total</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>127</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>(derived: 41% of 310)</t>
-        </is>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="G45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Gap</t>
+          <t>Claim</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OI8869</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>310</t>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>Around 25 million people in Kenya still light their homes with kerosene or have no electricity at all.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Permanent Employees: Total</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>310</v>
+          <t xml:space="preserve">metrics: </t>
+        </is>
       </c>
       <c r="G46" t="inlineStr"/>
     </row>
@@ -3452,17 +3417,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>outcome</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>Around 25 million people in Kenya still light their homes with kerosene or have no electricity at all.</t>
+          <t>We have connected 42,000 households across 14 counties, replacing kerosene lamps and reducing household energy spend by 30%.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">metrics: </t>
+          <t>metrics: PI7954</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -3478,14 +3443,14 @@
           <t>outcome</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>We have connected 42,000 households across 14 counties, replacing kerosene lamps and reducing household energy spend by 30%.</t>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Our systems avoided an estimated 20,000 tCO2e in 2024.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>metrics: PI7954</t>
+          <t>metrics: OI2764</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -3501,14 +3466,14 @@
           <t>outcome</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Our systems avoided an estimated 20,000 tCO2e in 2024.</t>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>Repayment rates stay above 92% and we employ 310 staff, of whom 41% are women.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>metrics: OI2764</t>
+          <t>metrics: OI8869,OI6213</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -3526,12 +3491,12 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Repayment rates stay above 92% and we employ 310 staff, of whom 41% are women.</t>
+          <t>Who we serve 62% of our customers live below the national poverty line according to the Poverty Probability Index, and 71% had no electricity before buying from us.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>metrics: OI8869,OI6213</t>
+          <t xml:space="preserve">metrics: </t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -3549,7 +3514,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>Who we serve 62% of our customers live below the national poverty line according to the Poverty Probability Index, and 71% had no electricity before buying from us.</t>
+          <t>A 2025 study by an independent evaluator compared customers with a matched control group and found 18% higher evening study hours for children and lower reported respiratory symptoms.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3572,7 +3537,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>A 2025 study by an independent evaluator compared customers with a matched control group and found 18% higher evening study hours for children and lower reported respiratory symptoms.</t>
+          <t>Over-indebtedness: we cap instalments at 10% of estimated household income and offer payment holidays after crop failures.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3590,12 +3555,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>outcome</t>
+          <t>intent</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Over-indebtedness: we cap instalments at 10% of estimated household income and offer payment holidays after crop failures.</t>
+          <t>Over the next three years we target 150,000 connected households and 80,000 tCO2e avoided per year, and we report against IRIS+, SDG 7/1/13 and the GOGLA impact metrics.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,12 +3578,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>intent</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>Over the next three years we target 150,000 connected households and 80,000 tCO2e avoided per year, and we report against IRIS+, SDG 7/1/13 and the GOGLA impact metrics.</t>
+          <t>Our carbon methodology is verified by a third-party auditor under Gold Standard rules.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3628,31 +3593,8 @@
       </c>
       <c r="G54" t="inlineStr"/>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Claim</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>Our carbon methodology is verified by a third-party auditor under Gold Standard rules.</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metrics: </t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G55"/>
+  <autoFilter ref="A1:G54"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3694,7 +3636,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 3 of 21 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
+          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 2 of 21 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3720,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3 of 21</t>
+          <t>2 of 21</t>
         </is>
       </c>
     </row>
@@ -3912,13 +3854,13 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>evidence: estimated</t>
+          <t>evidence: partial</t>
         </is>
       </c>
     </row>
@@ -4037,7 +3979,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SDG 8 alignment</t>
+          <t>SDG 5 alignment</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4093,7 +4035,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SDG 9 alignment</t>
+          <t>SDG 8 alignment</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4121,7 +4063,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SDG 2 alignment</t>
+          <t>SDG 9 alignment</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -4177,7 +4119,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SDG 6 alignment</t>
+          <t>SDG 2 alignment</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4205,7 +4147,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SDG 15 alignment</t>
+          <t>SDG 3 alignment</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4233,7 +4175,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SDG 3 alignment</t>
+          <t>SDG 4 alignment</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -4261,7 +4203,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SDG 5 alignment</t>
+          <t>SDG 6 alignment</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4289,7 +4231,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SDG 4 alignment</t>
+          <t>SDG 10 alignment</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4317,7 +4259,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SDG 10 alignment</t>
+          <t>SDG 12 alignment</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4345,7 +4287,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SDG 12 alignment</t>
+          <t>SDG 15 alignment</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4573,7 +4515,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Methodology v1.1.0 · config 8fabf9b5a7e2 (effective 2026-10-07).</t>
+          <t>Methodology v1.2.0 · config ae3e77ecaccf (effective 2026-10-08).</t>
         </is>
       </c>
     </row>
@@ -4633,7 +4575,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 3 of 21 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
+          <t>Automated analysis: produced by rules and a deterministic scoring model; no generative AI was used. 2 of 21 scores are estimated from document text rather than reported metrics. Review before relying on it.</t>
         </is>
       </c>
     </row>

--- a/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
+++ b/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08T15:56:23Z</t>
+          <t>2026-10-08T16:14:45Z</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-08T15:56:23Z</t>
+          <t>2026-10-08T16:14:45Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>

--- a/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
+++ b/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08T16:14:45Z</t>
+          <t>2026-10-08T19:53:04Z</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-08T16:14:45Z</t>
+          <t>2026-10-08T19:53:04Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>

--- a/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
+++ b/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08T19:53:04Z</t>
+          <t>2026-10-08T20:03:48Z</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-08T19:53:04Z</t>
+          <t>2026-10-08T20:03:48Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>

--- a/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
+++ b/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
@@ -21,8 +21,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'5 Dimensions'!$A$1:$E$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'SDG Alignment'!$A$1:$G$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Gap Analysis'!$A$1:$F$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Claims'!$A$1:$F$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All figures'!$A$1:$G$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Claims'!$A$1:$F$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All figures'!$A$1:$G$53</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'AI provenance'!$A$13:$F$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Methodology'!$A$1:$B$12</definedName>
   </definedNames>
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-08T20:03:48Z</t>
+          <t>2026-10-09T05:02:01Z</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -585,7 +585,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Depth=1.5, Duration=1.5</t>
+          <t>Depth=2.1, Duration=2.1</t>
         </is>
       </c>
     </row>
@@ -828,11 +828,11 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1857,12 +1857,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>outcome</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>Around 25 million people in Kenya still light their homes with kerosene or have no electricity at all.</t>
+          <t>We have connected 42,000 households across 14 counties, replacing kerosene lamps and reducing household energy spend by 30%.</t>
         </is>
       </c>
       <c r="C2" s="6" t="n">
@@ -1871,7 +1871,11 @@
       <c r="D2" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>PI7954</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>regex</t>
@@ -1884,9 +1888,9 @@
           <t>outcome</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>We have connected 42,000 households across 14 counties, replacing kerosene lamps and reducing household energy spend by 30%.</t>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Our systems avoided an estimated 20,000 tCO2e in 2024.</t>
         </is>
       </c>
       <c r="C3" s="6" t="n">
@@ -1897,7 +1901,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PI7954</t>
+          <t>OI2764</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1912,9 +1916,9 @@
           <t>outcome</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Our systems avoided an estimated 20,000 tCO2e in 2024.</t>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Repayment rates stay above 92% and we employ 310 staff, of whom 41% are women.</t>
         </is>
       </c>
       <c r="C4" s="6" t="n">
@@ -1925,7 +1929,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>OI2764</t>
+          <t>OI8869, OI6213</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1942,7 +1946,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Repayment rates stay above 92% and we employ 310 staff, of whom 41% are women.</t>
+          <t>Who we serve 62% of our customers live below the national poverty line according to the Poverty Probability Index, and 71% had no electricity before buying from us.</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
@@ -1951,11 +1955,7 @@
       <c r="D5" s="7" t="n">
         <v>0.3</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>OI8869, OI6213</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>regex</t>
@@ -1970,14 +1970,14 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Who we serve 62% of our customers live below the national poverty line according to the Poverty Probability Index, and 71% had no electricity before buying from us.</t>
+          <t>A 2025 study by an independent evaluator compared customers with a matched control group and found 18% higher evening study hours for children and lower reported respiratory symptoms.</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
@@ -1994,14 +1994,14 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>A 2025 study by an independent evaluator compared customers with a matched control group and found 18% higher evening study hours for children and lower reported respiratory symptoms.</t>
+          <t>Over-indebtedness: we cap instalments at 10% of estimated household income and offer payment holidays after crop failures.</t>
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
@@ -2013,12 +2013,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>outcome</t>
+          <t>intent</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Over-indebtedness: we cap instalments at 10% of estimated household income and offer payment holidays after crop failures.</t>
+          <t>Over the next three years we target 150,000 connected households and 80,000 tCO2e avoided per year, and we report against IRIS+, SDG 7/1/13 and the GOGLA impact metrics.</t>
         </is>
       </c>
       <c r="C8" s="6" t="n">
@@ -2037,19 +2037,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>intent</t>
+          <t>output</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Over the next three years we target 150,000 connected households and 80,000 tCO2e avoided per year, and we report against IRIS+, SDG 7/1/13 and the GOGLA impact metrics.</t>
+          <t>Our carbon methodology is verified by a third-party auditor under Gold Standard rules.</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
@@ -2058,32 +2058,8 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Our carbon methodology is verified by a third-party auditor under Gold Standard rules.</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>regex</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F10"/>
+  <autoFilter ref="A1:F9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2094,7 +2070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G54"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2175,7 +2151,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-08T20:03:48Z</t>
+          <t>2026-10-09T05:02:01Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -2236,16 +2212,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.8/5.0</t>
+          <t>2.0/5.0</t>
         </is>
       </c>
       <c r="E6" s="5" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="F6" s="6" t="n">
         <v>5</v>
@@ -2368,16 +2344,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.5/5.0</t>
+          <t>2.1/5.0</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Depth=1.5, Duration=1.5</t>
+          <t>Depth=2.1, Duration=2.1</t>
         </is>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>5</v>
@@ -3394,17 +3370,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>outcome</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>Around 25 million people in Kenya still light their homes with kerosene or have no electricity at all.</t>
+          <t>We have connected 42,000 households across 14 counties, replacing kerosene lamps and reducing household energy spend by 30%.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">metrics: </t>
+          <t>metrics: PI7954</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -3420,14 +3396,14 @@
           <t>outcome</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>We have connected 42,000 households across 14 counties, replacing kerosene lamps and reducing household energy spend by 30%.</t>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Our systems avoided an estimated 20,000 tCO2e in 2024.</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>metrics: PI7954</t>
+          <t>metrics: OI2764</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -3443,14 +3419,14 @@
           <t>outcome</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Our systems avoided an estimated 20,000 tCO2e in 2024.</t>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>Repayment rates stay above 92% and we employ 310 staff, of whom 41% are women.</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>metrics: OI2764</t>
+          <t>metrics: OI8869,OI6213</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -3468,12 +3444,12 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>Repayment rates stay above 92% and we employ 310 staff, of whom 41% are women.</t>
+          <t>Who we serve 62% of our customers live below the national poverty line according to the Poverty Probability Index, and 71% had no electricity before buying from us.</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>metrics: OI8869,OI6213</t>
+          <t xml:space="preserve">metrics: </t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -3491,7 +3467,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Who we serve 62% of our customers live below the national poverty line according to the Poverty Probability Index, and 71% had no electricity before buying from us.</t>
+          <t>A 2025 study by an independent evaluator compared customers with a matched control group and found 18% higher evening study hours for children and lower reported respiratory symptoms.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3514,7 +3490,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>A 2025 study by an independent evaluator compared customers with a matched control group and found 18% higher evening study hours for children and lower reported respiratory symptoms.</t>
+          <t>Over-indebtedness: we cap instalments at 10% of estimated household income and offer payment holidays after crop failures.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3532,12 +3508,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>outcome</t>
+          <t>intent</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>Over-indebtedness: we cap instalments at 10% of estimated household income and offer payment holidays after crop failures.</t>
+          <t>Over the next three years we target 150,000 connected households and 80,000 tCO2e avoided per year, and we report against IRIS+, SDG 7/1/13 and the GOGLA impact metrics.</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3555,12 +3531,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>intent</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Over the next three years we target 150,000 connected households and 80,000 tCO2e avoided per year, and we report against IRIS+, SDG 7/1/13 and the GOGLA impact metrics.</t>
+          <t>Our carbon methodology is verified by a third-party auditor under Gold Standard rules.</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3570,31 +3546,8 @@
       </c>
       <c r="G53" t="inlineStr"/>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Claim</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>Our carbon methodology is verified by a third-party auditor under Gold Standard rules.</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">metrics: </t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G54"/>
+  <autoFilter ref="A1:G53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4371,7 +4324,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>9 impact claims</t>
+          <t>8 impact claims</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">

--- a/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
+++ b/demo/sunpath_energy_ltd/sunpath_energy_ltd_data.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-09T05:02:01Z</t>
+          <t>2026-10-09T09:37:46Z</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-10-09T05:02:01Z</t>
+          <t>2026-10-09T09:37:46Z</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
